--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -40,7 +40,7 @@
     <t>es/es/h/home.report.json</t>
   </si>
   <si>
-    <t>["hero-campaign","hero-branded","columns-category","columns-category"]</t>
+    <t>["hero-campaign","hero-campaign","hero-campaign","hero-campaign","hero-campaign","hero-campaign","hero-branded","columns-category","columns-category"]</t>
   </si>
   <si>
     <t>es/es/h/home</t>
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-06-04T13:54:40.389Z</t>
+    <t>2026-06-04T15:41:12.228Z</t>
   </si>
   <si>
     <t>Moda de Home 2026 | Mango Home España (Península y Baleares)</t>
